--- a/SGC-CKN/Excel/94f9565a-0acd-4b20-8d0f-ef9622ea3e0d_Thi_công_cọc_khoan_nhồi_TN-B4-B2_74_D1200_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/94f9565a-0acd-4b20-8d0f-ef9622ea3e0d_Thi_công_cọc_khoan_nhồi_TN-B4-B2_74_D1200_21-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="127">
   <si>
     <t>Dự án</t>
   </si>
@@ -23,16 +23,19 @@
     <t>Hạng mục</t>
   </si>
   <si>
+    <t>Khách sạn GrandHyatt</t>
+  </si>
+  <si>
+    <t>Tên bộ phận</t>
+  </si>
+  <si>
     <t>Thi công cọc khoan nhồi</t>
   </si>
   <si>
-    <t>Tên bộ phận</t>
-  </si>
-  <si>
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TN-B4-B2.74</t>
+    <t>B2.74</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -127,10 +130,10 @@
     <t>Mẫu M4</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét pha - cát pha màu xám xanh, xám đen, trạng thái dẻo chảy đến chảy</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">16:18
@@ -140,6 +143,9 @@
     <t>Mẫu M5</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t xml:space="preserve">16:28
 20/03/2026</t>
   </si>
@@ -147,6 +153,9 @@
     <t>Mẫu M6</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t xml:space="preserve">10:00
 21/03/2026</t>
   </si>
@@ -158,6 +167,9 @@
     <t>Mẫu M7</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t xml:space="preserve">10:20
 21/03/2026</t>
   </si>
@@ -165,6 +177,9 @@
     <t>Mẫu M8</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t xml:space="preserve">10:30
 21/03/2026</t>
   </si>
@@ -172,6 +187,9 @@
     <t>Mẫu M9</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t xml:space="preserve">10:40
 21/03/2026</t>
   </si>
@@ -179,6 +197,9 @@
     <t>Mẫu M10</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t xml:space="preserve">10:55
 21/03/2026</t>
   </si>
@@ -186,6 +207,9 @@
     <t>Mẫu M11</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:10
 21/03/2026</t>
   </si>
@@ -193,6 +217,9 @@
     <t>Mẫu M12</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:30
 21/03/2026</t>
   </si>
@@ -200,10 +227,7 @@
     <t>Mẫu M13</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Sét - Sét pha màu xám xanh, xám ghi, xám vàng, nâu đỏ, trạng thái dẻo cứng đến nửa cứng</t>
+    <t>Sét pha, xám xanh, xám đen, xám ghi, xám vàng, nâu đỏ, TT dẻo cứng đến nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">11:50
@@ -213,6 +237,9 @@
     <t>Mẫu M14</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t xml:space="preserve">13:50
 21/03/2026</t>
   </si>
@@ -224,14 +251,14 @@
     <t>Mẫu M15</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t xml:space="preserve">14:28
 21/03/2026</t>
   </si>
   <si>
     <t>Mẫu M16</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>Cát hạt mịn màu xám ghi, xám vàng, kết cấu chặt đến rất chặt</t>
@@ -1117,7 +1144,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1131,10 +1158,10 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1148,10 +1175,10 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1165,10 +1192,10 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1182,10 +1209,10 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1199,10 +1226,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1217,54 +1244,54 @@
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
         <v>4.15</v>
@@ -1282,24 +1309,24 @@
         <v>3.24</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" s="5">
         <v>2.1</v>
@@ -1317,24 +1344,24 @@
         <v>11.94</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" s="5">
         <v>0.11</v>
@@ -1352,24 +1379,24 @@
         <v>13.26</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" s="5">
         <v>-2.1</v>
@@ -1387,24 +1414,24 @@
         <v>11.94</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" s="10">
         <v>-4.09</v>
@@ -1422,24 +1449,24 @@
         <v>12.06</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F16" s="10">
         <v>-6.1</v>
@@ -1457,24 +1484,24 @@
         <v>11.88</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F17" s="10">
         <v>-8.08</v>
@@ -1492,24 +1519,24 @@
         <v>12.12</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F18" s="10">
         <v>-10.1</v>
@@ -1527,24 +1554,24 @@
         <v>12.06</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F19" s="10">
         <v>-12.11</v>
@@ -1562,24 +1589,24 @@
         <v>12.06</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F20" s="10">
         <v>-14.12</v>
@@ -1597,24 +1624,24 @@
         <v>11.82</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F21" s="10">
         <v>-16.09</v>
@@ -1632,24 +1659,24 @@
         <v>8.04</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F22" s="10">
         <v>-18.1</v>
@@ -1667,24 +1694,24 @@
         <v>8.08</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F23" s="10">
         <v>-20.12</v>
@@ -1702,24 +1729,24 @@
         <v>5.94</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F24" s="13">
         <v>-22.1</v>
@@ -1737,24 +1764,24 @@
         <v>6</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F25" s="13">
         <v>-24.1</v>
@@ -1772,24 +1799,24 @@
         <v>5.91</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F26" s="13">
         <v>-26.07</v>
@@ -1807,24 +1834,24 @@
         <v>6.7</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F27" s="16">
         <v>-28.08</v>
@@ -1842,24 +1869,24 @@
         <v>12</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F28" s="16">
         <v>-30.08</v>
@@ -1877,24 +1904,24 @@
         <v>10.1</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F29" s="16">
         <v>-32.099999999999994</v>
@@ -1912,24 +1939,24 @@
         <v>7.96</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F30" s="16">
         <v>-34.08999999999999</v>
@@ -1947,24 +1974,24 @@
         <v>9.9</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F31" s="16">
         <v>-36.069999999999986</v>
@@ -1982,24 +2009,24 @@
         <v>6.03</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F32" s="16">
         <v>-38.079999999999984</v>
@@ -2017,24 +2044,24 @@
         <v>9.23</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F33" s="16">
         <v>-40.079999999999984</v>
@@ -2052,24 +2079,24 @@
         <v>3.45</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F34" s="16">
         <v>-42.08999999999998</v>
@@ -2087,24 +2114,24 @@
         <v>4.8</v>
       </c>
       <c r="K34" s="17" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F35" s="16">
         <v>-44.08999999999998</v>
@@ -2122,24 +2149,24 @@
         <v>5.94</v>
       </c>
       <c r="K35" s="17" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F36" s="16">
         <v>-46.06999999999998</v>
@@ -2157,24 +2184,24 @@
         <v>6.03</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F37" s="16">
         <v>-48.07999999999998</v>
@@ -2192,24 +2219,24 @@
         <v>6.03</v>
       </c>
       <c r="K37" s="17" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F38" s="16">
         <v>-50.089999999999975</v>
@@ -2227,24 +2254,24 @@
         <v>5.97</v>
       </c>
       <c r="K38" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F39" s="16">
         <v>-52.07999999999998</v>
@@ -2262,24 +2289,24 @@
         <v>5.97</v>
       </c>
       <c r="K39" s="17" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F40" s="16">
         <v>-54.06999999999998</v>
@@ -2297,24 +2324,24 @@
         <v>6.03</v>
       </c>
       <c r="K40" s="17" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F41" s="16">
         <v>-56.07999999999998</v>
@@ -2332,24 +2359,24 @@
         <v>6.06</v>
       </c>
       <c r="K41" s="17" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F42" s="16">
         <v>-58.09999999999998</v>
@@ -2367,24 +2394,24 @@
         <v>5.94</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F43" s="16">
         <v>-60.07999999999998</v>
@@ -2402,24 +2429,24 @@
         <v>5.97</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F44" s="16">
         <v>-62.06999999999998</v>
@@ -2437,24 +2464,24 @@
         <v>4.82</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F45" s="16">
         <v>-64.07999999999998</v>
@@ -2472,12 +2499,12 @@
         <v>3.1</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
@@ -2583,31 +2610,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2615,10 +2642,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>4</v>
@@ -2644,10 +2671,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="10">
         <v>9</v>
@@ -2673,10 +2700,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D4" s="13">
         <v>3</v>
@@ -2702,10 +2729,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D5" s="16">
         <v>19</v>
@@ -2728,13 +2755,13 @@
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D6" s="21">
         <v>35</v>
